--- a/要件定義.xlsx
+++ b/要件定義.xlsx
@@ -5,15 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aswell-C108\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aswell-C108\Desktop\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448821A7-9BB6-4583-9684-88AFD5885857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C14423-51FE-4442-986E-9D8BF343641A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0872306B-905B-48AE-BA14-0D918F80446E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{0872306B-905B-48AE-BA14-0D918F80446E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="基本要件" sheetId="1" r:id="rId1"/>
+    <sheet name="機能要件" sheetId="2" r:id="rId2"/>
+    <sheet name="非機能要件" sheetId="3" r:id="rId3"/>
+    <sheet name="スケジュール" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="85">
   <si>
     <t>顧客管理システム</t>
   </si>
@@ -301,13 +305,435 @@
   <si>
     <t>HTTPSによる暗号化通信が必須条件。</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>U</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Create</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作成</t>
+    <rPh sb="0" eb="2">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Read</t>
+  </si>
+  <si>
+    <t>参照</t>
+    <rPh sb="0" eb="2">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Update</t>
+  </si>
+  <si>
+    <t>更新</t>
+    <rPh sb="0" eb="2">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Delete</t>
+  </si>
+  <si>
+    <t>削除</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>合計</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小合計</t>
+    <rPh sb="0" eb="1">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ゴウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小合計</t>
+    <rPh sb="0" eb="3">
+      <t>ショウゴウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お客様名前：azwell保育園　　 商談相手：保育園　園長先生</t>
+    <rPh sb="1" eb="3">
+      <t>キャクサマ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ホイクエン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ショウダン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>ホイクエン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>エンチョウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>センセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1. シンプルなビジネスモデル設定</t>
+  </si>
+  <si>
+    <r>
+      <t>商品：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> おむつ（S/M/L）、おしりふき、除菌シートの3種類のみ。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>顧客（B）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 地元の小規模保育園。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>サービス：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 毎月定額、または使った分だけ納品するシンプルな契約。</t>
+    </r>
+  </si>
+  <si>
+    <t>2. データベースの構成（最小限のカラム）</t>
+  </si>
+  <si>
+    <t>機能を「簡単」にするために、テーブルのカラム（項目）を必要最低限に絞ります。</t>
+  </si>
+  <si>
+    <r>
+      <t>customers</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（保育園）テーブル</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 園名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>child_count</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 園児数（おむつの消費スピードを予測するのに使います）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>address</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 住所</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 状況（「契約中」「商談中」の2択にする）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>items</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（商品）テーブル</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 商品名（おむつLサイズ、など）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>stock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 自社在庫数</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 単価</t>
+    </r>
+  </si>
+  <si>
+    <t>3. パワーアップ機能（ここだけこだわる！）</t>
+  </si>
+  <si>
+    <r>
+      <t>機能を減らす代わりに、以下の</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1点だけ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を「自動計算」でパワーアップさせます。</t>
+    </r>
+  </si>
+  <si>
+    <t>「そろそろ注文が来るはず」予測機能</t>
+  </si>
+  <si>
+    <r>
+      <t>計算式：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>園児数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> × </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>1日5枚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> × </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>30日</t>
+    </r>
+  </si>
+  <si>
+    <t>前回の納品日から計算して、在庫が切れそうな園を一覧で「要連絡」と赤く表示させる。</t>
+  </si>
+  <si>
+    <t>これがあるだけで、営業マンにとって「今日どこに電話すべきか」がすぐわかる便利なシステムになります。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,6 +748,37 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -352,7 +809,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -361,6 +818,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -377,6 +855,148 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>6640</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>95537</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08EBA59A-6184-A20D-4E33-E7A3EB23B8A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="5645440" cy="5581937"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>635000</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>597170</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>177977</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56A81905-CE4D-9435-D333-C5F7C9853E18}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5613400" y="1314450"/>
+          <a:ext cx="5245370" cy="3435527"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>482862</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>133486</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{669658A9-B57B-F454-68B5-B40A46458CE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="5105662" cy="2648086"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -697,23 +1317,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60B647A0-9CA2-4D44-A374-562CD10F84A3}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="47.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="104.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -721,7 +1344,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -729,12 +1352,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -742,7 +1365,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -750,12 +1373,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -763,7 +1386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -771,12 +1394,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -784,7 +1407,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -792,7 +1415,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -800,7 +1423,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2">
       <c r="A15" s="2" t="s">
         <v>36</v>
       </c>
@@ -808,7 +1431,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2">
       <c r="A16" s="2" t="s">
         <v>39</v>
       </c>
@@ -816,12 +1439,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -829,12 +1452,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -842,7 +1465,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -850,7 +1473,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -858,12 +1481,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -871,12 +1494,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>43</v>
       </c>
@@ -884,22 +1507,446 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>31</v>
       </c>
       <c r="B29" t="s">
         <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A246E5D-6651-4631-BAE0-2C3E448E0D98}">
+  <dimension ref="I2:K5"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="9:11">
+      <c r="I2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="9:11">
+      <c r="I3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="9:11">
+      <c r="I4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="9:11">
+      <c r="I5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1C33224-D872-4A0A-A1FC-926FDF87CF23}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAA0343B-1B14-4A3D-BBE0-F87243369A9F}">
+  <dimension ref="A13:H20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="13" spans="1:7">
+      <c r="A13" s="3">
+        <v>46139</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C13" s="3">
+        <v>46142</v>
+      </c>
+      <c r="D13" s="3">
+        <v>46143</v>
+      </c>
+      <c r="E13" s="3">
+        <v>46149</v>
+      </c>
+      <c r="F13" s="3">
+        <v>46150</v>
+      </c>
+      <c r="G13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>6</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <f>SUM(A14:F14)</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="3">
+        <v>46153</v>
+      </c>
+      <c r="B15" s="3">
+        <v>46154</v>
+      </c>
+      <c r="C15" s="3">
+        <v>46155</v>
+      </c>
+      <c r="D15" s="3">
+        <v>46156</v>
+      </c>
+      <c r="E15" s="3">
+        <v>46157</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1">
+        <v>6</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>6</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+      <c r="G16">
+        <f>SUM(A16:F16)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="3">
+        <v>46160</v>
+      </c>
+      <c r="B17" s="3">
+        <v>46161</v>
+      </c>
+      <c r="C17" s="3">
+        <v>46162</v>
+      </c>
+      <c r="D17" s="3">
+        <v>46163</v>
+      </c>
+      <c r="E17" s="3">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1">
+        <v>6</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18" s="1">
+        <v>6</v>
+      </c>
+      <c r="G18">
+        <f>SUM(A18:F18)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="3">
+        <v>46167</v>
+      </c>
+      <c r="B19" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C19" s="3">
+        <v>46169</v>
+      </c>
+      <c r="G19" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20">
+        <v>6</v>
+      </c>
+      <c r="B20">
+        <v>6</v>
+      </c>
+      <c r="C20">
+        <v>6</v>
+      </c>
+      <c r="G20">
+        <f>SUM(A20:F20)</f>
+        <v>18</v>
+      </c>
+      <c r="H20">
+        <f>SUM(G14,G16,G18,G20)</f>
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79AB0886-2141-4FD7-BF5A-C3339D9DC0DF}">
+  <dimension ref="A1:A48"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="22">
+      <c r="A1" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="5"/>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="5"/>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="5"/>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="22">
+      <c r="A11" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="5"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="5"/>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="5"/>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="5"/>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="5"/>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="5"/>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="5"/>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="5"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="5"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="22">
+      <c r="A36" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="5"/>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="5"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="5"/>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="7"/>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="7"/>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="7"/>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="7" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
